--- a/Document/Data/属性表.xlsx
+++ b/Document/Data/属性表.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="174">
   <si>
     <t>百分比 P
 数值 V
@@ -368,6 +368,12 @@
     <t>质能打印机打印物品的速度（倍率）</t>
   </si>
   <si>
+    <t>百分比 P
+数值 V
+单位数值 U
+词条 T</t>
+  </si>
+  <si>
     <t>暴击率</t>
   </si>
   <si>
@@ -416,6 +422,132 @@
     <t>角色移动的速度</t>
   </si>
   <si>
+    <t>异常状态</t>
+  </si>
+  <si>
+    <t>眩晕</t>
+  </si>
+  <si>
+    <t>Stun</t>
+  </si>
+  <si>
+    <r>
+      <t>&gt;=100时，进入</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>眩晕状态</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>，无法行动</t>
+    </r>
+  </si>
+  <si>
+    <t>流血</t>
+  </si>
+  <si>
+    <t>Bleed</t>
+  </si>
+  <si>
+    <r>
+      <t>&gt;=100时，进入</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>流血状态</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>，每秒损失一定生命值</t>
+    </r>
+  </si>
+  <si>
+    <t>过载</t>
+  </si>
+  <si>
+    <t>Overload</t>
+  </si>
+  <si>
+    <r>
+      <t>&gt;=100时，进入</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>过载状态</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>，无法使用模块技能</t>
+    </r>
+  </si>
+  <si>
+    <t>过热</t>
+  </si>
+  <si>
+    <t>Overheat</t>
+  </si>
+  <si>
+    <r>
+      <t>&gt;=100时，进入</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>过热状态</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>，损失核心属性，冷却降低</t>
+    </r>
+  </si>
+  <si>
     <t>防具提供</t>
   </si>
   <si>
@@ -444,6 +576,105 @@
   </si>
   <si>
     <t>降低结构类型伤害的能力</t>
+  </si>
+  <si>
+    <t>伤害词条</t>
+  </si>
+  <si>
+    <t>物理伤害</t>
+  </si>
+  <si>
+    <t>PhysicalDamage</t>
+  </si>
+  <si>
+    <t>物理类型伤害</t>
+  </si>
+  <si>
+    <t>能量伤害</t>
+  </si>
+  <si>
+    <t>EnergyDamage</t>
+  </si>
+  <si>
+    <t>能量类型伤害</t>
+  </si>
+  <si>
+    <t>结构伤害</t>
+  </si>
+  <si>
+    <t>StructureDamage</t>
+  </si>
+  <si>
+    <t>结构类型伤害</t>
+  </si>
+  <si>
+    <t>冲击</t>
+  </si>
+  <si>
+    <t>Impact</t>
+  </si>
+  <si>
+    <t>物理伤害词条，可累计眩晕值</t>
+  </si>
+  <si>
+    <t>眩晕值</t>
+  </si>
+  <si>
+    <t>切割</t>
+  </si>
+  <si>
+    <t>Cutting</t>
+  </si>
+  <si>
+    <t>物理伤害词条，可累计流血值</t>
+  </si>
+  <si>
+    <t>流血值</t>
+  </si>
+  <si>
+    <t>电能</t>
+  </si>
+  <si>
+    <t>Electricity</t>
+  </si>
+  <si>
+    <t>能量伤害词条，可累计过载值</t>
+  </si>
+  <si>
+    <t>过载值</t>
+  </si>
+  <si>
+    <t>热能</t>
+  </si>
+  <si>
+    <t>Heat</t>
+  </si>
+  <si>
+    <t>能量伤害词条，可累计过热值</t>
+  </si>
+  <si>
+    <t>过热值</t>
+  </si>
+  <si>
+    <t>粒子</t>
+  </si>
+  <si>
+    <t>Particle</t>
+  </si>
+  <si>
+    <t>T</t>
+  </si>
+  <si>
+    <t>结构伤害词条，将结构伤害直接作用于生命值</t>
+  </si>
+  <si>
+    <t>分解</t>
+  </si>
+  <si>
+    <t>Decompose</t>
+  </si>
+  <si>
+    <t>结构伤害词条，按比例降低所有抗性</t>
   </si>
 </sst>
 </file>
@@ -456,10 +687,62 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="30">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="4"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="9" tint="-0.25"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="4"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="5" tint="-0.25"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -473,14 +756,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -627,6 +902,12 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -952,150 +1233,177 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1415,182 +1723,182 @@
   <dimension ref="A1:E12"/>
   <sheetFormatPr defaultColWidth="15.5555555555556" defaultRowHeight="24" customHeight="1" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="15.5555555555556" style="1"/>
-    <col min="2" max="2" width="19.2222222222222" style="1" customWidth="1"/>
-    <col min="3" max="3" width="20" style="1" customWidth="1"/>
-    <col min="4" max="4" width="13" style="1" customWidth="1"/>
-    <col min="5" max="5" width="56.5555555555556" style="1" customWidth="1"/>
-    <col min="6" max="6" width="45.2222222222222" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="15.5555555555556" style="1" customWidth="1"/>
+    <col min="1" max="1" width="15.5555555555556" style="2"/>
+    <col min="2" max="2" width="19.2222222222222" style="2" customWidth="1"/>
+    <col min="3" max="3" width="20" style="2" customWidth="1"/>
+    <col min="4" max="4" width="13" style="2" customWidth="1"/>
+    <col min="5" max="5" width="56.5555555555556" style="2" customWidth="1"/>
+    <col min="6" max="6" width="45.2222222222222" style="2" customWidth="1"/>
+    <col min="7" max="16384" width="15.5555555555556" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="56" customHeight="1" spans="1:5">
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="7" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" s="3" customFormat="1" customHeight="1" spans="1:5">
-      <c r="B2" s="3" t="s">
+    <row r="2" s="13" customFormat="1" customHeight="1" spans="1:5">
+      <c r="B2" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="13" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" ht="34" customHeight="1" spans="1:5">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="D3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="7" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="4" customHeight="1" spans="1:5">
-      <c r="A4" s="3"/>
-      <c r="B4" s="1" t="s">
+      <c r="A4" s="13"/>
+      <c r="B4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" s="1" t="s">
+      <c r="D4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="5" customHeight="1" spans="1:5">
-      <c r="A5" s="3"/>
-      <c r="B5" s="1" t="s">
+      <c r="A5" s="13"/>
+      <c r="B5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" s="2" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="6" customHeight="1" spans="1:5">
-      <c r="A6" s="3"/>
-      <c r="B6" s="1" t="s">
+      <c r="A6" s="13"/>
+      <c r="B6" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" s="2" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="1:5">
-      <c r="A7" s="3"/>
-      <c r="B7" s="1" t="s">
+      <c r="A7" s="13"/>
+      <c r="B7" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E7" s="2" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="8" ht="40" customHeight="1" spans="1:5">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E8" s="5" t="s">
+      <c r="D8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" s="14" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="1:5">
-      <c r="A9" s="3"/>
-      <c r="B9" s="1" t="s">
+      <c r="A9" s="13"/>
+      <c r="B9" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E9" s="1" t="s">
+      <c r="D9" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="1:5">
-      <c r="A10" s="3"/>
-      <c r="B10" s="1" t="s">
+      <c r="A10" s="13"/>
+      <c r="B10" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E10" s="2" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="1:5">
-      <c r="A11" s="3"/>
-      <c r="B11" s="1" t="s">
+      <c r="A11" s="13"/>
+      <c r="B11" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D11" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="E11" s="2" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="1:5">
-      <c r="A12" s="3"/>
-      <c r="B12" s="1" t="s">
+      <c r="A12" s="13"/>
+      <c r="B12" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D12" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="E12" s="2" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1613,133 +1921,133 @@
   <dimension ref="B1:F8"/>
   <sheetFormatPr defaultColWidth="15.6666666666667" defaultRowHeight="24" customHeight="1" outlineLevelRow="7" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="15.6666666666667" style="1" customWidth="1"/>
-    <col min="2" max="2" width="18.7777777777778" style="1" customWidth="1"/>
-    <col min="3" max="3" width="16.6666666666667" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15.6666666666667" style="1" customWidth="1"/>
-    <col min="5" max="5" width="52.7777777777778" style="1" customWidth="1"/>
-    <col min="6" max="6" width="40.5555555555556" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="15.6666666666667" style="1" customWidth="1"/>
+    <col min="1" max="1" width="15.6666666666667" style="2" customWidth="1"/>
+    <col min="2" max="2" width="18.7777777777778" style="2" customWidth="1"/>
+    <col min="3" max="3" width="16.6666666666667" style="2" customWidth="1"/>
+    <col min="4" max="4" width="15.6666666666667" style="2" customWidth="1"/>
+    <col min="5" max="5" width="52.7777777777778" style="2" customWidth="1"/>
+    <col min="6" max="6" width="40.5555555555556" style="2" customWidth="1"/>
+    <col min="7" max="16384" width="15.6666666666667" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="48" customHeight="1" spans="2:6">
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="7" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" s="3" customFormat="1" customHeight="1" spans="2:6">
-      <c r="B2" s="3" t="s">
+    <row r="2" s="13" customFormat="1" customHeight="1" spans="2:6">
+      <c r="B2" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="13" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="3" ht="49" customHeight="1" spans="2:6">
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" s="1" t="s">
+      <c r="D3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="2" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="4" ht="49" customHeight="1" spans="2:6">
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" s="1" t="s">
+      <c r="D4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" s="2" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="5" ht="49" customHeight="1" spans="2:6">
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" s="1" t="s">
+      <c r="D5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" s="2" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="6" ht="49" customHeight="1" spans="2:6">
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E6" s="1" t="s">
+      <c r="D6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="F6" s="2" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="7" ht="49" customHeight="1" spans="2:6">
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E7" s="1" t="s">
+      <c r="D7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="F7" s="2" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="8" ht="49" customHeight="1" spans="2:6">
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E8" s="1" t="s">
+      <c r="D8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="F8" s="2" t="s">
         <v>62</v>
       </c>
     </row>
@@ -1760,214 +2068,214 @@
   <dimension ref="A1:F20"/>
   <sheetFormatPr defaultColWidth="14.6666666666667" defaultRowHeight="35" customHeight="1" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="2" width="14.6666666666667" style="1" customWidth="1"/>
-    <col min="3" max="3" width="21.2222222222222" style="1" customWidth="1"/>
-    <col min="4" max="4" width="14.6666666666667" style="1" customWidth="1"/>
-    <col min="5" max="5" width="49.3333333333333" style="1" customWidth="1"/>
-    <col min="6" max="6" width="35.2222222222222" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="14.6666666666667" style="1" customWidth="1"/>
+    <col min="1" max="2" width="14.6666666666667" style="2" customWidth="1"/>
+    <col min="3" max="3" width="21.2222222222222" style="2" customWidth="1"/>
+    <col min="4" max="4" width="14.6666666666667" style="2" customWidth="1"/>
+    <col min="5" max="5" width="49.3333333333333" style="2" customWidth="1"/>
+    <col min="6" max="6" width="35.2222222222222" style="2" customWidth="1"/>
+    <col min="7" max="16384" width="14.6666666666667" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="68" customHeight="1" spans="1:6">
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="7" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:6">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3" t="s">
+      <c r="A2" s="13"/>
+      <c r="B2" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3" t="s">
+      <c r="C2" s="13"/>
+      <c r="D2" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="13" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" s="1" t="s">
+      <c r="D3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:6">
-      <c r="A4" s="3"/>
-      <c r="B4" s="1" t="s">
+      <c r="A4" s="13"/>
+      <c r="B4" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" s="1" t="s">
+      <c r="D4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1" spans="1:6">
-      <c r="A5" s="3"/>
-      <c r="B5" s="1" t="s">
+      <c r="A5" s="13"/>
+      <c r="B5" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" s="2" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1" spans="1:6">
-      <c r="A6" s="3"/>
-      <c r="B6" s="1" t="s">
+      <c r="A6" s="13"/>
+      <c r="B6" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" s="2" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:6">
-      <c r="A7" s="3"/>
-      <c r="B7" s="1" t="s">
+      <c r="A7" s="13"/>
+      <c r="B7" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E7" s="2" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E8" s="1" t="s">
+      <c r="D8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1" spans="1:6">
-      <c r="A9" s="3"/>
-      <c r="B9" s="1" t="s">
+      <c r="A9" s="13"/>
+      <c r="B9" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E9" s="1" t="s">
+      <c r="D9" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:6">
-      <c r="A10" s="3"/>
-      <c r="B10" s="1" t="s">
+      <c r="A10" s="13"/>
+      <c r="B10" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E10" s="2" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:6">
-      <c r="A11" s="3"/>
-      <c r="B11" s="1" t="s">
+      <c r="A11" s="13"/>
+      <c r="B11" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D11" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="E11" s="2" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:6">
-      <c r="A12" s="3"/>
-      <c r="B12" s="1" t="s">
+      <c r="A12" s="13"/>
+      <c r="B12" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D12" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="E12" s="2" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="13" ht="28" customHeight="1" spans="1:6">
-      <c r="B13" s="1" t="s">
+      <c r="B13" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D13" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="E13" s="2" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="14" ht="28" customHeight="1" spans="1:6">
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="D14" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="E14" s="2" t="s">
         <v>100</v>
       </c>
     </row>
@@ -1993,188 +2301,389 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F38"/>
-  <sheetFormatPr defaultColWidth="15.2222222222222" defaultRowHeight="14.4" outlineLevelCol="5"/>
+  <dimension ref="A1:G42"/>
+  <sheetFormatPr defaultColWidth="15.2222222222222" defaultRowHeight="15.6" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="14.1111111111111" style="1" customWidth="1"/>
-    <col min="2" max="2" width="21.7777777777778" style="1" customWidth="1"/>
-    <col min="3" max="3" width="24.7777777777778" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15.2222222222222" style="1" customWidth="1"/>
-    <col min="5" max="5" width="50.3333333333333" style="1" customWidth="1"/>
-    <col min="6" max="6" width="31.3333333333333" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="15.2222222222222" style="1" customWidth="1"/>
+    <col min="1" max="1" width="14.1111111111111" style="2" customWidth="1"/>
+    <col min="2" max="2" width="21.7777777777778" style="3" customWidth="1"/>
+    <col min="3" max="3" width="24.7777777777778" style="2" customWidth="1"/>
+    <col min="4" max="4" width="15.2222222222222" style="2" customWidth="1"/>
+    <col min="5" max="5" width="55.6666666666667" style="2" customWidth="1"/>
+    <col min="6" max="6" width="43.3333333333333" style="2" customWidth="1"/>
+    <col min="7" max="7" width="41.8888888888889" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="15.2222222222222" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="54" customHeight="1" spans="1:6">
-      <c r="D1" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" ht="27" customHeight="1" spans="1:6">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3" t="s">
+    <row r="1" ht="73" customHeight="1" spans="1:6">
+      <c r="D1" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="27" customHeight="1" spans="1:6">
+      <c r="A2" s="5"/>
+      <c r="B2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3" t="s">
+      <c r="C2" s="5"/>
+      <c r="D2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="5" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="3" ht="27" customHeight="1" spans="1:6">
-      <c r="B3" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="C3" s="1" t="s">
+      <c r="B3" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="C3" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>103</v>
+      <c r="E3" s="2" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="4" ht="27" customHeight="1" spans="1:6">
-      <c r="B4" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="C4" s="1" t="s">
+      <c r="B4" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="C4" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>106</v>
+      <c r="E4" s="2" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="5" ht="35" customHeight="1" spans="1:6">
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="D5" s="1" t="s">
+      <c r="C5" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>108</v>
+      <c r="E5" s="7" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="6" ht="27" customHeight="1" spans="1:6">
-      <c r="B6" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="C6" s="1" t="s">
+      <c r="B6" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="C6" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>111</v>
+      <c r="E6" s="7" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="7" ht="27" customHeight="1" spans="1:6">
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="D7" s="1" t="s">
+      <c r="C7" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>113</v>
+      <c r="E7" s="2" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="8" ht="27" customHeight="1" spans="1:6">
-      <c r="B8" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="C8" s="1" t="s">
+      <c r="B8" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E8" s="1" t="s">
+      <c r="C8" s="2" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="9" ht="27" customHeight="1"/>
-    <row r="10" ht="27" customHeight="1"/>
-    <row r="11" ht="27" customHeight="1"/>
+      <c r="D8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="9" ht="27" customHeight="1" spans="1:6">
+      <c r="A9" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="10" ht="27" customHeight="1" spans="1:6">
+      <c r="A10" s="8"/>
+      <c r="B10" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="11" ht="27" customHeight="1" spans="1:6">
+      <c r="A11" s="8"/>
+      <c r="B11" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>127</v>
+      </c>
+    </row>
     <row r="12" ht="27" customHeight="1" spans="1:6">
-      <c r="A12" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="13" ht="27" customHeight="1" spans="1:6">
-      <c r="A13" s="4"/>
-      <c r="B13" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="14" ht="27" customHeight="1" spans="1:6">
-      <c r="A14" s="4"/>
-      <c r="B14" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
+      <c r="A12" s="8"/>
+      <c r="B12" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="13" ht="27" customHeight="1"/>
+    <row r="14" ht="27" customHeight="1"/>
     <row r="15" ht="27" customHeight="1"/>
-    <row r="16" ht="27" customHeight="1"/>
-    <row r="17" ht="27" customHeight="1"/>
-    <row r="18" ht="27" customHeight="1"/>
+    <row r="16" ht="27" customHeight="1" spans="1:6">
+      <c r="A16" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="17" ht="27" customHeight="1" spans="1:6">
+      <c r="A17" s="8"/>
+      <c r="B17" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="18" ht="27" customHeight="1" spans="1:6">
+      <c r="A18" s="8"/>
+      <c r="B18" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>140</v>
+      </c>
+    </row>
     <row r="19" ht="27" customHeight="1"/>
-    <row r="20" ht="27" customHeight="1"/>
-    <row r="21" ht="27" customHeight="1"/>
-    <row r="22" ht="27" customHeight="1"/>
-    <row r="23" ht="27" customHeight="1"/>
-    <row r="24" ht="27" customHeight="1"/>
-    <row r="25" ht="27" customHeight="1"/>
-    <row r="26" ht="27" customHeight="1"/>
-    <row r="27" ht="27" customHeight="1"/>
-    <row r="28" ht="27" customHeight="1"/>
-    <row r="29" ht="27" customHeight="1"/>
+    <row r="20" ht="27" customHeight="1" spans="1:6">
+      <c r="A20" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="21" ht="27" customHeight="1" spans="1:6">
+      <c r="A21" s="8"/>
+      <c r="B21" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="22" ht="27" customHeight="1" spans="1:6">
+      <c r="A22" s="8"/>
+      <c r="B22" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="23" ht="27" customHeight="1" spans="1:6">
+      <c r="A23" s="8"/>
+    </row>
+    <row r="24" ht="27" customHeight="1" spans="1:6">
+      <c r="A24" s="8"/>
+      <c r="B24" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="25" ht="27" customHeight="1" spans="1:6">
+      <c r="A25" s="8"/>
+      <c r="B25" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="26" ht="27" customHeight="1" spans="1:6">
+      <c r="A26" s="8"/>
+      <c r="B26" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="27" ht="27" customHeight="1" spans="1:6">
+      <c r="A27" s="8"/>
+      <c r="B27" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="28" ht="27" customHeight="1" spans="1:6">
+      <c r="A28" s="8"/>
+      <c r="B28" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="29" ht="27" customHeight="1" spans="1:6">
+      <c r="A29" s="8"/>
+      <c r="B29" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>173</v>
+      </c>
+    </row>
     <row r="30" ht="27" customHeight="1"/>
     <row r="31" ht="27" customHeight="1"/>
     <row r="32" ht="27" customHeight="1"/>
@@ -2184,11 +2693,18 @@
     <row r="36" ht="27" customHeight="1"/>
     <row r="37" ht="27" customHeight="1"/>
     <row r="38" ht="27" customHeight="1"/>
+    <row r="39" ht="27" customHeight="1"/>
+    <row r="40" ht="27" customHeight="1"/>
+    <row r="41" ht="27" customHeight="1"/>
+    <row r="42" ht="27" customHeight="1"/>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="6">
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="B2:C2"/>
-    <mergeCell ref="A12:A14"/>
+    <mergeCell ref="A9:A12"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A20:A29"/>
+    <mergeCell ref="G9:G12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
